--- a/data/run_ab.xlsx
+++ b/data/run_ab.xlsx
@@ -524,10 +524,10 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>1002.313595775</v>
+        <v>1002.008263876225</v>
       </c>
       <c r="H2" t="n">
-        <v>1.401326201279921</v>
+        <v>1.401497593358524</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -559,29 +559,29 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>153.71851360446</v>
+        <v>153.8821471640656</v>
       </c>
       <c r="C3" t="n">
-        <v>1148.197074234486</v>
+        <v>1218.597577512264</v>
       </c>
       <c r="D3" t="n">
         <v>163468.0278</v>
       </c>
       <c r="E3" t="n">
-        <v>1029771.090250331</v>
+        <v>1074117.508714112</v>
       </c>
       <c r="F3" t="n">
-        <v>1503.273234344108</v>
+        <v>1483.929206040197</v>
       </c>
       <c r="G3" t="n">
-        <v>1243.150389587259</v>
+        <v>1268.642823336422</v>
       </c>
       <c r="H3" t="n">
-        <v>1.300233882129428</v>
+        <v>1.292436642229587</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>products</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -590,16 +590,16 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>860.0470742344856</v>
+        <v>930.4475775122643</v>
       </c>
       <c r="L3" t="n">
         <v>63156.27779999998</v>
       </c>
       <c r="M3" t="n">
-        <v>1029771.090250331</v>
+        <v>1074117.508714112</v>
       </c>
       <c r="N3" t="n">
-        <v>1500.388256592897</v>
+        <v>1481.044228288985</v>
       </c>
     </row>
     <row r="4">
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>160.2291276934984</v>
+        <v>160.6791521030508</v>
       </c>
       <c r="C4" t="n">
         <v>2450</v>
@@ -618,16 +618,16 @@
         <v>155294.62641</v>
       </c>
       <c r="E4" t="n">
-        <v>2723715.441698822</v>
+        <v>2835746.629663931</v>
       </c>
       <c r="F4" t="n">
-        <v>2498.985514619197</v>
+        <v>2518.397126481691</v>
       </c>
       <c r="G4" t="n">
-        <v>1352.53</v>
+        <v>1455.83955625</v>
       </c>
       <c r="H4" t="n">
-        <v>1.269412511932565</v>
+        <v>1.245599024507198</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -646,10 +646,10 @@
         <v>54982.87640999997</v>
       </c>
       <c r="M4" t="n">
-        <v>2723715.441698822</v>
+        <v>2835746.629663931</v>
       </c>
       <c r="N4" t="n">
-        <v>2496.100536867985</v>
+        <v>2515.51214873048</v>
       </c>
     </row>
     <row r="5">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>160.2291276934984</v>
+        <v>160.6791521030508</v>
       </c>
       <c r="C5" t="n">
         <v>2450</v>
@@ -668,16 +668,16 @@
         <v>152188.7338818</v>
       </c>
       <c r="E5" t="n">
-        <v>2723715.441698822</v>
+        <v>2835746.629663931</v>
       </c>
       <c r="F5" t="n">
-        <v>2504.78475973646</v>
+        <v>2524.196371598955</v>
       </c>
       <c r="G5" t="n">
-        <v>1352.53</v>
+        <v>1455.83955625</v>
       </c>
       <c r="H5" t="n">
-        <v>1.269412511932565</v>
+        <v>1.245599024507198</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -696,10 +696,10 @@
         <v>51876.98388179997</v>
       </c>
       <c r="M5" t="n">
-        <v>2723715.441698822</v>
+        <v>2835746.629663931</v>
       </c>
       <c r="N5" t="n">
-        <v>2501.899781985249</v>
+        <v>2521.311393847744</v>
       </c>
     </row>
     <row r="6">
@@ -724,10 +724,10 @@
         <v>2.884977751211491</v>
       </c>
       <c r="G6" t="n">
-        <v>1002.313595775</v>
+        <v>1002.008263876225</v>
       </c>
       <c r="H6" t="n">
-        <v>1.401326201279921</v>
+        <v>1.401497593358524</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -762,22 +762,22 @@
         <v>150</v>
       </c>
       <c r="C7" t="n">
-        <v>344.2642809823155</v>
+        <v>344.2001828923821</v>
       </c>
       <c r="D7" t="n">
         <v>175545.5625</v>
       </c>
       <c r="E7" t="n">
-        <v>56401.33152682893</v>
+        <v>56399.06568133821</v>
       </c>
       <c r="F7" t="n">
-        <v>21.06954575697489</v>
+        <v>21.07179320572104</v>
       </c>
       <c r="G7" t="n">
-        <v>1007.906834832523</v>
+        <v>1010.546900773356</v>
       </c>
       <c r="H7" t="n">
-        <v>1.39821223715776</v>
+        <v>1.396759140767428</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -790,16 +790,16 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>56.11428098231556</v>
+        <v>56.05018289238217</v>
       </c>
       <c r="L7" t="n">
         <v>75233.8125</v>
       </c>
       <c r="M7" t="n">
-        <v>56401.33152682893</v>
+        <v>56399.06568133821</v>
       </c>
       <c r="N7" t="n">
-        <v>18.1845680057634</v>
+        <v>18.18681545450955</v>
       </c>
     </row>
     <row r="8">
@@ -812,22 +812,22 @@
         <v>95.54140127388536</v>
       </c>
       <c r="C8" t="n">
-        <v>369.9003821238875</v>
+        <v>369.7427185252309</v>
       </c>
       <c r="D8" t="n">
         <v>217237.63359375</v>
       </c>
       <c r="E8" t="n">
-        <v>82272.64649599389</v>
+        <v>82263.03495465945</v>
       </c>
       <c r="F8" t="n">
-        <v>32.38255185846904</v>
+        <v>32.38585990705198</v>
       </c>
       <c r="G8" t="n">
-        <v>1010.441177578178</v>
+        <v>1014.641848080168</v>
       </c>
       <c r="H8" t="n">
-        <v>1.396817127112574</v>
+        <v>1.394526138586409</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -840,16 +840,16 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>81.75038212388756</v>
+        <v>81.59271852523091</v>
       </c>
       <c r="L8" t="n">
         <v>116925.88359375</v>
       </c>
       <c r="M8" t="n">
-        <v>82272.64649599389</v>
+        <v>82263.03495465945</v>
       </c>
       <c r="N8" t="n">
-        <v>29.49757410725755</v>
+        <v>29.50088215584049</v>
       </c>
     </row>
     <row r="9">
@@ -862,22 +862,22 @@
         <v>95.54140127388536</v>
       </c>
       <c r="C9" t="n">
-        <v>815.8121138811111</v>
+        <v>803.8048967719078</v>
       </c>
       <c r="D9" t="n">
         <v>2752835.2929</v>
       </c>
       <c r="E9" t="n">
-        <v>542347.5496748937</v>
+        <v>539871.1285909641</v>
       </c>
       <c r="F9" t="n">
-        <v>117.3447796517406</v>
+        <v>118.029702934405</v>
       </c>
       <c r="G9" t="n">
-        <v>1052.420590019846</v>
+        <v>1096.759689707324</v>
       </c>
       <c r="H9" t="n">
-        <v>1.375052229786431</v>
+        <v>1.354514576157032</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -890,16 +890,16 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>527.6621138811112</v>
+        <v>515.6548967719078</v>
       </c>
       <c r="L9" t="n">
         <v>2652523.5429</v>
       </c>
       <c r="M9" t="n">
-        <v>542347.5496748937</v>
+        <v>539871.1285909641</v>
       </c>
       <c r="N9" t="n">
-        <v>114.4598019005291</v>
+        <v>115.1447251831935</v>
       </c>
     </row>
     <row r="10">
@@ -909,7 +909,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>99.25991487834534</v>
+        <v>99.42354843795094</v>
       </c>
       <c r="C10" t="n">
         <v>2000</v>
@@ -918,16 +918,16 @@
         <v>2587665.175326</v>
       </c>
       <c r="E10" t="n">
-        <v>2122367.005288256</v>
+        <v>2186801.328024609</v>
       </c>
       <c r="F10" t="n">
-        <v>1420.358005319736</v>
+        <v>1418.294621658791</v>
       </c>
       <c r="G10" t="n">
-        <v>1319.32</v>
+        <v>1426</v>
       </c>
       <c r="H10" t="n">
-        <v>1.278080025661575</v>
+        <v>1.252033533812935</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -946,10 +946,10 @@
         <v>2487353.425326</v>
       </c>
       <c r="M10" t="n">
-        <v>2122367.005288256</v>
+        <v>2186801.328024609</v>
       </c>
       <c r="N10" t="n">
-        <v>1417.473027568525</v>
+        <v>1415.40964390758</v>
       </c>
     </row>
     <row r="11">
@@ -959,25 +959,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>99.25991487834534</v>
+        <v>99.42354843795094</v>
       </c>
       <c r="C11" t="n">
-        <v>1657.305115461349</v>
+        <v>1685.180482268333</v>
       </c>
       <c r="D11" t="n">
-        <v>978845.1111495176</v>
+        <v>994344.9201061744</v>
       </c>
       <c r="E11" t="n">
-        <v>1675054.420336681</v>
+        <v>1742619.608617999</v>
       </c>
       <c r="F11" t="n">
-        <v>1454.156749698699</v>
+        <v>1451.260051886896</v>
       </c>
       <c r="G11" t="n">
-        <v>1290.769287737871</v>
+        <v>1393.827051266041</v>
       </c>
       <c r="H11" t="n">
-        <v>1.285990011647858</v>
+        <v>1.259359926224191</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -990,16 +990,16 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>1369.155115461349</v>
+        <v>1397.030482268333</v>
       </c>
       <c r="L11" t="n">
-        <v>878533.3611495176</v>
+        <v>894033.1701061744</v>
       </c>
       <c r="M11" t="n">
-        <v>1675054.420336681</v>
+        <v>1742619.608617999</v>
       </c>
       <c r="N11" t="n">
-        <v>1451.271771947488</v>
+        <v>1448.375074135685</v>
       </c>
     </row>
     <row r="12">
@@ -1009,25 +1009,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>99.25991487834534</v>
+        <v>99.42354843795094</v>
       </c>
       <c r="C12" t="n">
-        <v>1570.863124728203</v>
+        <v>1605.215865373611</v>
       </c>
       <c r="D12" t="n">
-        <v>751254.4250182046</v>
+        <v>767386.5531834213</v>
       </c>
       <c r="E12" t="n">
-        <v>1563806.970994971</v>
+        <v>1631566.024421179</v>
       </c>
       <c r="F12" t="n">
-        <v>1461.180073031861</v>
+        <v>1458.119427873348</v>
       </c>
       <c r="G12" t="n">
-        <v>1283.122457985857</v>
+        <v>1383.585845251684</v>
       </c>
       <c r="H12" t="n">
-        <v>1.288185557979385</v>
+        <v>1.261782250491932</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1040,16 +1040,16 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>1282.713124728203</v>
+        <v>1317.065865373611</v>
       </c>
       <c r="L12" t="n">
-        <v>650942.6750182046</v>
+        <v>667074.8031834213</v>
       </c>
       <c r="M12" t="n">
-        <v>1563806.970994971</v>
+        <v>1631566.024421179</v>
       </c>
       <c r="N12" t="n">
-        <v>1458.29509528065</v>
+        <v>1455.234450122137</v>
       </c>
     </row>
     <row r="13">
@@ -1062,22 +1062,22 @@
         <v>54.45859872611464</v>
       </c>
       <c r="C13" t="n">
-        <v>344.2642809823155</v>
+        <v>344.2001828923821</v>
       </c>
       <c r="D13" t="n">
         <v>168523.74</v>
       </c>
       <c r="E13" t="n">
-        <v>56401.33152682893</v>
+        <v>56399.06568133821</v>
       </c>
       <c r="F13" t="n">
-        <v>32.78761644313835</v>
+        <v>32.78986389188449</v>
       </c>
       <c r="G13" t="n">
-        <v>1007.906834832523</v>
+        <v>1010.546900773356</v>
       </c>
       <c r="H13" t="n">
-        <v>1.39821223715776</v>
+        <v>1.396759140767428</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1090,16 +1090,16 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>56.11428098231556</v>
+        <v>56.05018289238217</v>
       </c>
       <c r="L13" t="n">
         <v>68211.98999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>56401.33152682893</v>
+        <v>56399.06568133821</v>
       </c>
       <c r="N13" t="n">
-        <v>29.90263869192686</v>
+        <v>29.904886140673</v>
       </c>
     </row>
   </sheetData>
@@ -1113,7 +1113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>116838.0575325749</v>
+        <v>117343.3097470404</v>
       </c>
     </row>
     <row r="3">
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>116838.0575325749</v>
+        <v>117343.3097470404</v>
       </c>
     </row>
     <row r="4">
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8181611851328574</v>
+        <v>0.8246634108416941</v>
       </c>
     </row>
     <row r="5">
@@ -1165,7 +1165,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>778.920383550499</v>
+        <v>1228.19330868569</v>
       </c>
     </row>
     <row r="6">
@@ -1175,7 +1175,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.75496213264801e-05</v>
+        <v>9.100776282918969e-05</v>
       </c>
     </row>
     <row r="7">
@@ -1185,107 +1185,117 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>729.1936192594509</v>
+        <v>730.2957988712086</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>W_fan_W</t>
+          <t>V_freestream_mps</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8460199.729024339</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>W_hpc_W</t>
+          <t>W_fan_W</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>43956200.94065922</v>
+        <v>8459859.852200732</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>W_lpc_W</t>
+          <t>W_hpc_W</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2471781.684952066</v>
+        <v>43720518.50028389</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>choked</t>
+          <t>W_lpc_W</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>2471079.866877826</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>f_ab</t>
+          <t>choked</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0423541311737583</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>f_main</t>
+          <t>f_ab</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.03892044239334775</v>
+        <v>0.04417019819549572</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>m_fuel_kgps</t>
+          <t>f_main</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10.22912769349842</v>
+        <v>0.04063314031721973</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>pe_exit_Pa</t>
+          <t>m_fuel_kgps</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>101324.9999990065</v>
+        <v>10.6791521030508</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>w_hpt_Jpkg</t>
+          <t>pe_exit_Pa</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>447312.5231346461</v>
+        <v>101324.9999999947</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>w_hpt_Jpkg</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>444181.8924501344</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>w_lpt_Jpkg</t>
         </is>
       </c>
-      <c r="B17" t="n">
-        <v>111247.379994198</v>
+      <c r="B18" t="n">
+        <v>111053.7033234665</v>
       </c>
     </row>
   </sheetData>
@@ -1317,7 +1327,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Tt4</t>
+          <t>TIT</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -1327,7 +1337,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>afterburn.Tt7</t>
+          <t>afterburn.TAB</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -1457,7 +1467,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>eta_burner</t>
+          <t>diffuser_pr</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1467,121 +1477,121 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>eta_fan</t>
+          <t>eta_burner</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.89</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>eta_hpc</t>
+          <t>eta_fan</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.86</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>eta_hpt</t>
+          <t>eta_hpc</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>eta_lpc</t>
+          <t>eta_hpt</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>eta_lpt</t>
+          <t>eta_lpc</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>eta_mech</t>
+          <t>eta_lpt</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.99</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>eta_nozzle</t>
+          <t>eta_mech</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>fan_pr</t>
+          <t>eta_nozzle</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.75</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>fuel_LHV</t>
+          <t>fan_pr</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>43150000</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>hpc_duct_pr</t>
+          <t>fuel_LHV</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.99</v>
+        <v>43150000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>hpc_pr</t>
+          <t>hpc_duct_pr</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>12.8</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>inlet_pr</t>
+          <t>hpc_pr</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.99</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="29">
